--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API목록" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컴포넌트목록'!$A$1:$J$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컴포넌트목록'!$A$1:$L$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -71,12 +71,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0FFF0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3ECF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,6 +107,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E0F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,7 +159,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,13 +168,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C11"/>
+  <dimension ref="B2:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -633,6 +657,18 @@
       <c r="C11" s="3" t="inlineStr">
         <is>
           <t>P1 RCCS코어 / P2 설계·Run / P3 원가·문서 / P4 Toolbox·AI / P5 ERP·모바일</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>구축 현황 기준</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07 — 개발 서버 edim.seekerslab.com (Ubuntu 24.04, Docker·nginx·HTTPS·ufw, MinIO·Jenkins 가동)</t>
         </is>
       </c>
     </row>
@@ -647,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -660,6 +696,8 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -713,6 +751,16 @@
           <t>Phase</t>
         </is>
       </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>구축 상태</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>구축 내역 (2026-07-07)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
@@ -763,6 +811,16 @@
           <t>P1~</t>
         </is>
       </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>프로토타입 배포</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>https://edim.seekerslab.com — Drawing Viewer·DXF/IFC 업로드·AI 생성(샘플 모드)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -813,6 +871,12 @@
           <t>P1~</t>
         </is>
       </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -863,6 +927,12 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -913,6 +983,12 @@
           <t>P1~</t>
         </is>
       </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -963,6 +1039,12 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -973,7 +1055,7 @@
           <t>GW-01</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>게이트웨이</t>
         </is>
@@ -1011,6 +1093,16 @@
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>개발 대체 구축</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>nginx 1.24 — TLS(Let's Encrypt)·라우팅(/api·/jenkins·/minio/ui)·SPA 서빙</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1115,7 @@
           <t>SVC-01</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>게이트웨이</t>
         </is>
@@ -1063,6 +1155,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1073,7 +1171,7 @@
           <t>SVC-02</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1113,6 +1211,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -1123,7 +1227,7 @@
           <t>SVC-03</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1163,6 +1267,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1173,7 +1283,7 @@
           <t>SVC-04</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1211,6 +1321,16 @@
       <c r="J11" s="5" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 일부</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>FastAPI backend — DXF/IFC Import·DXF Export·DrawingDocument JSON</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1343,7 @@
           <t>SVC-05</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1263,6 +1383,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1273,7 +1399,7 @@
           <t>SVC-06</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1313,6 +1439,12 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -1323,7 +1455,7 @@
           <t>SVC-07</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1363,6 +1495,12 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1373,7 +1511,7 @@
           <t>SVC-08</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1413,6 +1551,12 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -1423,7 +1567,7 @@
           <t>SVC-09</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1463,6 +1607,12 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1473,7 +1623,7 @@
           <t>SVC-10</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1513,6 +1663,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -1523,7 +1679,7 @@
           <t>SVC-11</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1563,6 +1719,12 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1573,7 +1735,7 @@
           <t>SVC-12</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1613,6 +1775,12 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1623,7 +1791,7 @@
           <t>SVC-13</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>도메인 서비스</t>
         </is>
@@ -1663,6 +1831,12 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1673,7 +1847,7 @@
           <t>ENG-01</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>엔진</t>
         </is>
@@ -1713,6 +1887,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1723,7 +1903,7 @@
           <t>ENG-02</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>엔진</t>
         </is>
@@ -1763,6 +1943,12 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1773,7 +1959,7 @@
           <t>ENG-03</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>엔진</t>
         </is>
@@ -1811,6 +1997,16 @@
       <c r="J23" s="5" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 일부</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>ezdxf 기반 DXF(R2010) Export 경로 검증됨</t>
         </is>
       </c>
     </row>
@@ -1823,7 +2019,7 @@
           <t>AI-01</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
@@ -1861,6 +2057,16 @@
       <c r="J24" s="5" t="inlineStr">
         <is>
           <t>P4</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 일부</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Claude API 연동(ai_generator) — ANTHROPIC_API_KEY 미설정 시 샘플 모드</t>
         </is>
       </c>
     </row>
@@ -1873,7 +2079,7 @@
           <t>AI-02</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
@@ -1913,6 +2119,12 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1923,7 +2135,7 @@
           <t>AI-03</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
@@ -1963,6 +2175,12 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1973,7 +2191,7 @@
           <t>AI-04</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
@@ -2013,6 +2231,12 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -2023,7 +2247,7 @@
           <t>AI-05</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
@@ -2063,6 +2287,12 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -2073,7 +2303,7 @@
           <t>INT-01</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
@@ -2113,6 +2343,12 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -2123,7 +2359,7 @@
           <t>INT-02</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
@@ -2163,6 +2399,12 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -2173,7 +2415,7 @@
           <t>INT-03</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
@@ -2213,6 +2455,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -2223,7 +2471,7 @@
           <t>INT-04</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
@@ -2261,6 +2509,16 @@
       <c r="J32" s="5" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>DwgToDxfConverter 플러그블 인터페이스 — ODA 바이너리 미설치(501)</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2531,7 @@
           <t>INT-05</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
@@ -2313,6 +2571,12 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -2323,7 +2587,7 @@
           <t>INF-01</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
@@ -2363,6 +2627,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2373,7 +2643,7 @@
           <t>INF-02</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
@@ -2411,6 +2681,16 @@
       <c r="J35" s="5" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>구축완료</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>MinIO — S3 API 127.0.0.1:9000(내부), 콘솔 /minio/ui, 버킷 edim, 볼륨 minio_data</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2703,7 @@
           <t>INF-03</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
@@ -2463,6 +2743,12 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -2473,7 +2759,7 @@
           <t>INF-04</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
@@ -2513,6 +2799,12 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -2523,7 +2815,7 @@
           <t>INF-05</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
@@ -2563,6 +2855,12 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -2573,7 +2871,7 @@
           <t>INF-06</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
@@ -2611,6 +2909,16 @@
       <c r="J39" s="5" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>부분 구축</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Docker 29.6.1 + Compose v5.3, Jenkins LTS(/jenkins) — k8s는 운영 전환 시 도입</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2931,7 @@
           <t>INF-07</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
@@ -2663,9 +2971,15 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J40"/>
+  <autoFilter ref="A1:L40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컴포넌트목록'!$A$1:$L$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -632,7 +632,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>68개 (대표 엔드포인트)</t>
+          <t>80개 (대표 엔드포인트)</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings</t>
+          <t>/api/v1/codes/values/import-excel</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>도면 등록</t>
+          <t>코드 값 Excel Import (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/codes/groups/{id}/export-excel</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 조회 (block 파라미터)</t>
+          <t>Registered Code Table Export (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3488,17 +3488,17 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/drawings</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 저장</t>
+          <t>도면 등록</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/revisions</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>개정 생성</t>
+          <t>DrawingDocument 조회 (block 파라미터)</t>
         </is>
       </c>
     </row>
@@ -3538,17 +3538,17 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/dimensions</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>치수 등록 (Macro 바인딩)</t>
+          <t>DrawingDocument 저장</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/relations</t>
+          <t>/api/v1/drawings/{id}/revisions</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>부품 관계 등록</t>
+          <t>개정 생성</t>
         </is>
       </c>
     </row>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/import</t>
+          <t>/api/v1/drawings/{id}/dimensions</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>DXF/DWG/PDF/STEP Import</t>
+          <t>치수 등록 (Macro 바인딩)</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/export</t>
+          <t>/api/v1/drawings/{id}/relations</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>DXF/PDF Export</t>
+          <t>부품 관계 등록</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables</t>
+          <t>/api/v1/drawings/import</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Table 정의 생성</t>
+          <t>DXF/DWG/PDF/STEP Import</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/rows:bulk</t>
+          <t>/api/v1/drawings/{id}/export</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>행 일괄 입력</t>
+          <t>DXF/PDF Export</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/query</t>
+          <t>/api/v1/drawings/{id}/referencers</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>범위 조회 (Macro 참조용)</t>
+          <t>Where-used 역참조 조회 (DWG-026)</t>
         </is>
       </c>
     </row>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/import-excel</t>
+          <t>/api/v1/drawings/{id}/variants</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Excel Import</t>
+          <t>Variants 목록 (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms</t>
+          <t>/api/v1/drawings/{id}/supersede</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>UI Form 저장</t>
+          <t>대체 관계 등록 — old→new (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -3758,22 +3758,22 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}</t>
+          <t>/api/v1/tables</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Form 렌더 정의 조회</t>
+          <t>Table 정의 생성</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}/publish</t>
+          <t>/api/v1/tables/{id}/rows:bulk</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Form 게시 (승인 후)</t>
+          <t>행 일괄 입력</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/templets</t>
+          <t>/api/v1/tables/{id}/query</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Templet 목록</t>
+          <t>범위 조회 (Macro 참조용)</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections</t>
+          <t>/api/v1/tables/import-excel</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>선정 세션 생성</t>
+          <t>Excel Import</t>
         </is>
       </c>
     </row>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/slots</t>
+          <t>/api/v1/toolbox/forms</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Slot 값 선택</t>
+          <t>UI Form 저장</t>
         </is>
       </c>
     </row>
@@ -3883,22 +3883,22 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/finalize</t>
+          <t>/api/v1/toolbox/forms/{id}</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>완성품 Code 확정</t>
+          <t>Form 렌더 정의 조회</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
+          <t>/api/v1/toolbox/forms/{id}/publish</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>비규격 검토 요청</t>
+          <t>Form 게시 (승인 후)</t>
         </is>
       </c>
     </row>
@@ -3933,22 +3933,22 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/runs</t>
+          <t>/api/v1/toolbox/templets</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run 실행 요청</t>
+          <t>Templet 목록</t>
         </is>
       </c>
     </row>
@@ -3963,17 +3963,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}</t>
+          <t>/api/v1/cpq/selections</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Run 상태 조회</t>
+          <t>선정 세션 생성</t>
         </is>
       </c>
     </row>
@@ -3988,17 +3988,17 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}/outputs</t>
+          <t>/api/v1/cpq/selections/{id}/slots</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>산출물 목록</t>
+          <t>Slot 값 선택</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices</t>
+          <t>/api/v1/cpq/selections/{id}/finalize</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>단가 등록</t>
+          <t>완성품 Code 확정</t>
         </is>
       </c>
     </row>
@@ -4033,22 +4033,22 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices/resolve</t>
+          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>적용 단가 해석 (source 우선순위)</t>
+          <t>비규격 검토 요청</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/pcr</t>
+          <t>/api/v1/cpq/selections/{id}/runs</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>PCR 생성</t>
+          <t>EDIM Run 실행 요청</t>
         </is>
       </c>
     </row>
@@ -4083,22 +4083,22 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations</t>
+          <t>/api/v1/cpq/runs/{runId}</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>견적서 생성</t>
+          <t>Run 상태 조회</t>
         </is>
       </c>
     </row>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations/{id}/render</t>
+          <t>/api/v1/cpq/runs/{runId}/outputs</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>견적서 PDF 출력</t>
+          <t>산출물 목록</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/processes</t>
+          <t>/api/v1/cpq/runs/{runId}/bom/export</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>프로세스 정의 목록</t>
+          <t>BOM Excel Export (RUN-010)</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events</t>
+          <t>/api/v1/cost/prices</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>프로세스 이벤트 생성</t>
+          <t>단가 등록</t>
         </is>
       </c>
     </row>
@@ -4183,22 +4183,22 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events/{id}/status</t>
+          <t>/api/v1/cost/prices/resolve</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>이벤트 상태 전이</t>
+          <t>적용 단가 해석 (source 우선순위)</t>
         </is>
       </c>
     </row>
@@ -4208,22 +4208,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events</t>
+          <t>/api/v1/cost/pcr</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>업무함 (assignee/status 필터)</t>
+          <t>PCR 생성</t>
         </is>
       </c>
     </row>
@@ -4233,22 +4233,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/dashboard/project/{projectId}</t>
+          <t>/api/v1/cost/quotations</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 Dashboard 집계</t>
+          <t>견적서 생성</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/work-processes</t>
+          <t>/api/v1/cost/quotations/{id}/render</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Work Process 공정 데이터 등록</t>
+          <t>견적서 PDF 출력</t>
         </is>
       </c>
     </row>
@@ -4283,22 +4283,22 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals</t>
+          <t>/api/v1/erp/processes</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>승인 요청 생성</t>
+          <t>프로세스 정의 목록</t>
         </is>
       </c>
     </row>
@@ -4308,22 +4308,22 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/inbox</t>
+          <t>/api/v1/erp/events</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>승인함</t>
+          <t>프로세스 이벤트 생성</t>
         </is>
       </c>
     </row>
@@ -4333,22 +4333,22 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/{id}/decide</t>
+          <t>/api/v1/erp/events/{id}/status</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>승인/반려 결정</t>
+          <t>이벤트 상태 전이</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/history</t>
+          <t>/api/v1/erp/events</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>승인 이력</t>
+          <t>업무함 (assignee/status 필터)</t>
         </is>
       </c>
     </row>
@@ -4383,22 +4383,22 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/render</t>
+          <t>/api/v1/erp/dashboard/project/{projectId}</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Print Form + 데이터 → PDF</t>
+          <t>프로젝트 Dashboard 집계</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/export-office</t>
+          <t>/api/v1/erp/work-processes</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>xlsx/docx 내보내기</t>
+          <t>Work Process 공정 데이터 등록</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/upload-url</t>
+          <t>/api/v1/erp/supplier-code-maps</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>업로드 서명 URL</t>
+          <t>사용자↔공급자 코드 매핑 (ERP-018)</t>
         </is>
       </c>
     </row>
@@ -4458,22 +4458,22 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/{id}/download-url</t>
+          <t>/api/v1/approvals</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>다운로드 서명 URL</t>
+          <t>승인 요청 생성</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files</t>
+          <t>/api/v1/approvals/inbox</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Project Folder 파일 목록</t>
+          <t>승인함</t>
         </is>
       </c>
     </row>
@@ -4508,22 +4508,22 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications</t>
+          <t>/api/v1/approvals/{id}/decide</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>알림 목록</t>
+          <t>승인/반려 결정</t>
         </is>
       </c>
     </row>
@@ -4533,22 +4533,22 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications/read</t>
+          <t>/api/v1/approvals/history</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>읽음 처리</t>
+          <t>승인 이력</t>
         </is>
       </c>
     </row>
@@ -4558,22 +4558,22 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>/ws/notifications</t>
+          <t>/api/v1/documents/render</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>실시간 알림 채널</t>
+          <t>Print Form + 데이터 → PDF</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>ENG-01 Macro</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros/{id}/test-run</t>
+          <t>/api/v1/documents/export-office</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Macro Test Run (조건값→결과)</t>
+          <t>xlsx/docx 내보내기</t>
         </is>
       </c>
     </row>
@@ -4608,22 +4608,22 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/generate</t>
+          <t>/api/v1/doc-controls</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Prompt→Macro 생성</t>
+          <t>문서함 목록 — Released Status·Grade 필터 (DOC-001)</t>
         </is>
       </c>
     </row>
@@ -4633,22 +4633,22 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/convert</t>
+          <t>/api/v1/doc-controls/{id}/status</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>표현 간 변환 (from/to)</t>
+          <t>Released Status 전이 — Set-up→Check→Approve→Accepted</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/ui/suggest</t>
+          <t>/api/v1/doc-controls/allocate-code</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>UI Form 초안 제안</t>
+          <t>Document Code 채번 (DOC-003)</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-12 File</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/chat</t>
+          <t>/api/v1/files/upload-url</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>업로드 서명 URL</t>
         </is>
       </c>
     </row>
@@ -4708,27 +4708,327 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
+          <t>SVC-12 File</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/files/{id}/download-url</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>다운로드 서명 URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>SVC-12 File</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/files</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Project Folder 파일 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>SVC-13 Notify</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>알림 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>SVC-13 Notify</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/read</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>읽음 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>SVC-13 Notify</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>/ws/notifications</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>실시간 알림 채널</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>ENG-01 Macro</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/macros/{id}/test-run</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Macro Test Run (조건값→결과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/macro/generate</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>Prompt→Macro 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/macro/convert</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>표현 간 변환 (from/to)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/ui/suggest</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>UI Form 초안 제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/chat</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>사내 자료 챗봇</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>/api/v1/ai/learning/jobs</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>학습 잡 실행 (Platform 전용)</t>
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>INT-05 QR</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/qr/issue</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>도면·서류·Project·자산 QR 발급 (APP-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>INT-05 QR</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/qr/resolve</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>QR 해석 → 대상 링크·권한 검사</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E69"/>
+  <autoFilter ref="A1:E81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컴포넌트목록'!$A$1:$L$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -632,7 +632,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>80개 (대표 엔드포인트)</t>
+          <t>95개 (대표 엔드포인트 — 상세 스펙은 OpenAPI 원천, 개발표준 §3)</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3133,22 +3133,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/trees</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Tree 목록 (type 필터)</t>
+          <t>사용자 등록 (SYS-003)</t>
         </is>
       </c>
     </row>
@@ -3158,22 +3158,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}/children</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>하위 노드 조회</t>
+          <t>사용자 수정·상태 변경 (ACTIVE/LOCKED/RETIRED)</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes</t>
+          <t>/api/v1/roles</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>노드 생성 (승인 대상)</t>
+          <t>역할 생성·권한 부여 (SYS-004/005)</t>
         </is>
       </c>
     </row>
@@ -3208,22 +3208,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}/move</t>
+          <t>/api/v1/tenants</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>노드 이동 — Address 추적</t>
+          <t>테넌트 생성 — sys_tenant (ADM-001, Platform 전용)</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/resolve</t>
+          <t>/api/v1/hierarchy/trees</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>address→노드 해석</t>
+          <t>Tree 목록 (type 필터)</t>
         </is>
       </c>
     </row>
@@ -3258,22 +3258,22 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/groups</t>
+          <t>/api/v1/hierarchy/nodes/{id}/children</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>코드 그룹 등록</t>
+          <t>하위 노드 조회</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products</t>
+          <t>/api/v1/hierarchy/nodes</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Product Code 등록</t>
+          <t>노드 생성 (승인 대상)</t>
         </is>
       </c>
     </row>
@@ -3308,22 +3308,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products/{id}/check-duplicate</t>
+          <t>/api/v1/hierarchy/nodes/{id}/move</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Main Code 중복검토</t>
+          <t>노드 이동 — Address 추적</t>
         </is>
       </c>
     </row>
@@ -3333,22 +3333,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/relationships</t>
+          <t>/api/v1/hierarchy/resolve</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Mother-Child 관계 등록</t>
+          <t>address→노드 해석</t>
         </is>
       </c>
     </row>
@@ -3358,22 +3358,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products/{id}/expand</t>
+          <t>/api/v1/hierarchy/nodes/{id}</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>BOM 전개</t>
+          <t>노드 개명·속성 수정 (승인 대상)</t>
         </is>
       </c>
     </row>
@@ -3383,22 +3383,22 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/relationships/running-test</t>
+          <t>/api/v1/hierarchy/nodes/{id}</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Part List Running Test</t>
+          <t>노드 삭제 — DB 상호관계 점검 후</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/arrangements</t>
+          <t>/api/v1/codes/groups</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Arrangement 등록</t>
+          <t>코드 그룹 등록</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/values/import-excel</t>
+          <t>/api/v1/codes/products</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>코드 값 Excel Import (CODE-016)</t>
+          <t>Product Code 등록</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/groups/{id}/export-excel</t>
+          <t>/api/v1/codes/products/{id}/check-duplicate</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Registered Code Table Export (CODE-016)</t>
+          <t>Main Code 중복검토</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings</t>
+          <t>/api/v1/codes/relationships</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>도면 등록</t>
+          <t>Mother-Child 관계 등록</t>
         </is>
       </c>
     </row>
@@ -3508,22 +3508,22 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/codes/products/{id}/expand</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 조회 (block 파라미터)</t>
+          <t>BOM 전개</t>
         </is>
       </c>
     </row>
@@ -3533,22 +3533,22 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/codes/relationships/running-test</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 저장</t>
+          <t>Part List Running Test</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/revisions</t>
+          <t>/api/v1/codes/arrangements</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>개정 생성</t>
+          <t>Arrangement 등록</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/dimensions</t>
+          <t>/api/v1/codes/values/import-excel</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>치수 등록 (Macro 바인딩)</t>
+          <t>코드 값 Excel Import (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3608,22 +3608,22 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/relations</t>
+          <t>/api/v1/codes/groups/{id}/export-excel</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>부품 관계 등록</t>
+          <t>Registered Code Table Export (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/import</t>
+          <t>/api/v1/drawings</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>DXF/DWG/PDF/STEP Import</t>
+          <t>도면 등록</t>
         </is>
       </c>
     </row>
@@ -3663,17 +3663,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/export</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>DXF/PDF Export</t>
+          <t>DrawingDocument 조회 (block 파라미터)</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/referencers</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Where-used 역참조 조회 (DWG-026)</t>
+          <t>DrawingDocument 저장</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3713,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/variants</t>
+          <t>/api/v1/drawings/{id}/revisions</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Variants 목록 (DWG-027)</t>
+          <t>개정 생성</t>
         </is>
       </c>
     </row>
@@ -3743,12 +3743,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/supersede</t>
+          <t>/api/v1/drawings/{id}/dimensions</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>대체 관계 등록 — old→new (DWG-027)</t>
+          <t>치수 등록 (Macro 바인딩)</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables</t>
+          <t>/api/v1/drawings/{id}/relations</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Table 정의 생성</t>
+          <t>부품 관계 등록</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/rows:bulk</t>
+          <t>/api/v1/drawings/import</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>행 일괄 입력</t>
+          <t>DXF/DWG/PDF/STEP Import</t>
         </is>
       </c>
     </row>
@@ -3808,22 +3808,22 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/query</t>
+          <t>/api/v1/drawings/{id}/export</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>범위 조회 (Macro 참조용)</t>
+          <t>DXF/PDF Export</t>
         </is>
       </c>
     </row>
@@ -3833,22 +3833,22 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/import-excel</t>
+          <t>/api/v1/drawings/{id}/referencers</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Excel Import</t>
+          <t>Where-used 역참조 조회 (DWG-026)</t>
         </is>
       </c>
     </row>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms</t>
+          <t>/api/v1/drawings/{id}/variants</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>UI Form 저장</t>
+          <t>Variants 목록 (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -3883,22 +3883,22 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}</t>
+          <t>/api/v1/drawings/{id}/supersede</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Form 렌더 정의 조회</t>
+          <t>대체 관계 등록 — old→new (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -3908,22 +3908,22 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}/publish</t>
+          <t>/api/v1/drawings/{id}/dimensions/{dimId}</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Form 게시 (승인 후)</t>
+          <t>치수 Macro/Variant 바인딩 수정 (XOR 검증)</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/templets</t>
+          <t>/api/v1/parts</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Templet 목록</t>
+          <t>부품 마스터 목록·검색 (DWG-017)</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections</t>
+          <t>/api/v1/parts</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>선정 세션 생성</t>
+          <t>부품 등록</t>
         </is>
       </c>
     </row>
@@ -3983,22 +3983,22 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/slots</t>
+          <t>/api/v1/materials</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Slot 값 선택</t>
+          <t>재질 등록 — hazard_class 포함 (DWG-018)</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/finalize</t>
+          <t>/api/v1/tables</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>완성품 Code 확정</t>
+          <t>Table 정의 생성</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
+          <t>/api/v1/tables/{id}/rows:bulk</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>비규격 검토 요청</t>
+          <t>행 일괄 입력</t>
         </is>
       </c>
     </row>
@@ -4058,22 +4058,22 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/runs</t>
+          <t>/api/v1/tables/{id}/query</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run 실행 요청</t>
+          <t>범위 조회 (Macro 참조용)</t>
         </is>
       </c>
     </row>
@@ -4083,22 +4083,22 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}</t>
+          <t>/api/v1/tables/import-excel</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Run 상태 조회</t>
+          <t>Excel Import</t>
         </is>
       </c>
     </row>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}/outputs</t>
+          <t>/api/v1/toolbox/forms</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>산출물 목록</t>
+          <t>UI Form 저장</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}/bom/export</t>
+          <t>/api/v1/toolbox/forms/{id}</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>BOM Excel Export (RUN-010)</t>
+          <t>Form 렌더 정의 조회</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices</t>
+          <t>/api/v1/toolbox/forms/{id}/publish</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>단가 등록</t>
+          <t>Form 게시 (승인 후)</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices/resolve</t>
+          <t>/api/v1/toolbox/templets</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>적용 단가 해석 (source 우선순위)</t>
+          <t>Templet 목록</t>
         </is>
       </c>
     </row>
@@ -4208,22 +4208,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/pcr</t>
+          <t>/api/v1/cpq/selections</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>PCR 생성</t>
+          <t>선정 세션 목록 (project·상태 필터)</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations</t>
+          <t>/api/v1/cpq/selections</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>견적서 생성</t>
+          <t>선정 세션 생성</t>
         </is>
       </c>
     </row>
@@ -4258,22 +4258,22 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations/{id}/render</t>
+          <t>/api/v1/cpq/selections/{id}/slots</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>견적서 PDF 출력</t>
+          <t>Slot 값 선택</t>
         </is>
       </c>
     </row>
@@ -4283,22 +4283,22 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/processes</t>
+          <t>/api/v1/cpq/selections/{id}/finalize</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>프로세스 정의 목록</t>
+          <t>완성품 Code 확정</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events</t>
+          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>프로세스 이벤트 생성</t>
+          <t>비규격 검토 요청</t>
         </is>
       </c>
     </row>
@@ -4333,22 +4333,22 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events/{id}/status</t>
+          <t>/api/v1/cpq/selections/{id}/runs</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>이벤트 상태 전이</t>
+          <t>EDIM Run 실행 요청</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events</t>
+          <t>/api/v1/cpq/runs/{runId}</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>업무함 (assignee/status 필터)</t>
+          <t>Run 상태 조회</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/dashboard/project/{projectId}</t>
+          <t>/api/v1/cpq/runs/{runId}/outputs</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 Dashboard 집계</t>
+          <t>산출물 목록</t>
         </is>
       </c>
     </row>
@@ -4408,22 +4408,22 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/work-processes</t>
+          <t>/api/v1/cpq/runs/{runId}/bom/export</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Work Process 공정 데이터 등록</t>
+          <t>BOM Excel Export (RUN-010)</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/supplier-code-maps</t>
+          <t>/api/v1/cost/prices</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>사용자↔공급자 코드 매핑 (ERP-018)</t>
+          <t>단가 등록</t>
         </is>
       </c>
     </row>
@@ -4458,22 +4458,22 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals</t>
+          <t>/api/v1/cost/prices/resolve</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>승인 요청 생성</t>
+          <t>적용 단가 해석 (source 우선순위)</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4483,22 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/inbox</t>
+          <t>/api/v1/cost/pcr</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>승인함</t>
+          <t>PCR 생성</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/{id}/decide</t>
+          <t>/api/v1/cost/quotations</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>승인/반려 결정</t>
+          <t>견적서 생성</t>
         </is>
       </c>
     </row>
@@ -4533,22 +4533,22 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/history</t>
+          <t>/api/v1/cost/quotations/{id}/render</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>승인 이력</t>
+          <t>견적서 PDF 출력</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/render</t>
+          <t>/api/v1/projects</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Print Form + 데이터 → PDF</t>
+          <t>Project 등록 PS — 채번 (ERP-001)</t>
         </is>
       </c>
     </row>
@@ -4583,22 +4583,22 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/export-office</t>
+          <t>/api/v1/projects</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>xlsx/docx 내보내기</t>
+          <t>Project 목록 — 영업단계 필터</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls</t>
+          <t>/api/v1/erp/processes</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>문서함 목록 — Released Status·Grade 필터 (DOC-001)</t>
+          <t>프로세스 정의 목록</t>
         </is>
       </c>
     </row>
@@ -4633,22 +4633,22 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls/{id}/status</t>
+          <t>/api/v1/erp/process-defs</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Released Status 전이 — Set-up→Check→Approve→Accepted</t>
+          <t>프로세스 정의 생성 (W-14, ADMIN — 코드 신설은 Platform)</t>
         </is>
       </c>
     </row>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls/allocate-code</t>
+          <t>/api/v1/erp/process-defs/{id}</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Document Code 채번 (DOC-003)</t>
+          <t>정의 수정 — 선행/후행(edge)·기한·Form</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/upload-url</t>
+          <t>/api/v1/erp/events</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>업로드 서명 URL</t>
+          <t>프로세스 이벤트 생성</t>
         </is>
       </c>
     </row>
@@ -4708,22 +4708,22 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/{id}/download-url</t>
+          <t>/api/v1/erp/events/{id}/status</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>다운로드 서명 URL</t>
+          <t>이벤트 상태 전이</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files</t>
+          <t>/api/v1/erp/events</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Project Folder 파일 목록</t>
+          <t>업무함 (assignee/status 필터)</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications</t>
+          <t>/api/v1/erp/dashboard/project/{projectId}</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>알림 목록</t>
+          <t>프로젝트 Dashboard 집계</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications/read</t>
+          <t>/api/v1/erp/work-processes</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>읽음 처리</t>
+          <t>Work Process 공정 데이터 등록</t>
         </is>
       </c>
     </row>
@@ -4808,22 +4808,22 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>/ws/notifications</t>
+          <t>/api/v1/erp/supplier-code-maps</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>실시간 알림 채널</t>
+          <t>사용자↔공급자 코드 매핑 (ERP-018)</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>ENG-01 Macro</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros/{id}/test-run</t>
+          <t>/api/v1/approvals</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Macro Test Run (조건값→결과)</t>
+          <t>승인 요청 생성</t>
         </is>
       </c>
     </row>
@@ -4858,22 +4858,22 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/generate</t>
+          <t>/api/v1/approvals/inbox</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Prompt→Macro 생성</t>
+          <t>승인함</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/convert</t>
+          <t>/api/v1/approvals/{id}/decide</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>표현 간 변환 (from/to)</t>
+          <t>승인/반려 결정</t>
         </is>
       </c>
     </row>
@@ -4908,22 +4908,22 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/ui/suggest</t>
+          <t>/api/v1/approvals/history</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>UI Form 초안 제안</t>
+          <t>승인 이력</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/chat</t>
+          <t>/api/v1/documents/render</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>Print Form + 데이터 → PDF</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/learning/jobs</t>
+          <t>/api/v1/documents/export-office</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>학습 잡 실행 (Platform 전용)</t>
+          <t>xlsx/docx 내보내기</t>
         </is>
       </c>
     </row>
@@ -4983,22 +4983,22 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>INT-05 QR</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/qr/issue</t>
+          <t>/api/v1/doc-controls</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>도면·서류·Project·자산 QR 발급 (APP-001)</t>
+          <t>문서함 목록 — Released Status·Grade 필터 (DOC-001)</t>
         </is>
       </c>
     </row>
@@ -5008,27 +5008,402 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
+          <t>SVC-11 Print</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/doc-controls/{id}/status</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Released Status 전이 — Set-up→Check→Approve→Accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>SVC-11 Print</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/doc-controls/allocate-code</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Document Code 채번 (DOC-003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>SVC-12 File</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/files/upload-url</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>업로드 서명 URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>SVC-12 File</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/files/{id}/download-url</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>다운로드 서명 URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>SVC-12 File</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/files</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Project Folder 파일 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>SVC-13 Notify</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>알림 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>SVC-13 Notify</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/read</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>읽음 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>SVC-13 Notify</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>/ws/notifications</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>실시간 알림 채널</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>ENG-01 Macro</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/macros/{id}/test-run</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Macro Test Run (조건값→결과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/macro/generate</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Prompt→Macro 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/macro/convert</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>표현 간 변환 (from/to)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/ui/suggest</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>UI Form 초안 제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/chat</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>사내 자료 챗봇</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/learning/jobs</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>학습 잡 실행 (Platform 전용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
           <t>INT-05 QR</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/qr/issue</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>도면·서류·Project·자산 QR 발급 (APP-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>INT-05 QR</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>/api/v1/qr/resolve</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>QR 해석 → 대상 링크·권한 검사</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E81"/>
+  <autoFilter ref="A1:E96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컴포넌트목록'!$A$1:$L$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -632,7 +632,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>95개 (대표 엔드포인트 — 상세 스펙은 OpenAPI 원천, 개발표준 §3)</t>
+          <t>106개 (대표 엔드포인트 — 상세 스펙은 OpenAPI 원천, 개발표준 §3)</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3113,17 +3113,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/auth/permissions</t>
+          <t>/api/v1/auth/password</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>리소스별 권한 조회</t>
+          <t>비밀번호 변경 (정책 검증)</t>
         </is>
       </c>
     </row>
@@ -3138,17 +3138,17 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/auth/permissions</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>사용자 등록 (SYS-003)</t>
+          <t>리소스별 권한 조회</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/users/{id}</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>사용자 수정·상태 변경 (ACTIVE/LOCKED/RETIRED)</t>
+          <t>사용자 목록 (부서·상태 필터, ADMIN)</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/roles</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>역할 생성·권한 부여 (SYS-004/005)</t>
+          <t>사용자 등록 (SYS-003)</t>
         </is>
       </c>
     </row>
@@ -3213,17 +3213,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tenants</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>테넌트 생성 — sys_tenant (ADM-001, Platform 전용)</t>
+          <t>사용자 수정·상태 변경 (ACTIVE/LOCKED/RETIRED)</t>
         </is>
       </c>
     </row>
@@ -3233,22 +3233,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/trees</t>
+          <t>/api/v1/roles</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Tree 목록 (type 필터)</t>
+          <t>역할 생성·권한 부여 (SYS-004/005)</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}/children</t>
+          <t>/api/v1/tenants</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>하위 노드 조회</t>
+          <t>테넌트 목록·상태 (Platform 전용)</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes</t>
+          <t>/api/v1/tenants</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>노드 생성 (승인 대상)</t>
+          <t>테넌트 생성 — sys_tenant (ADM-001, Platform 전용)</t>
         </is>
       </c>
     </row>
@@ -3313,17 +3313,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}/move</t>
+          <t>/api/v1/hierarchy/trees</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>노드 이동 — Address 추적</t>
+          <t>Tree 목록 (type 필터)</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/resolve</t>
+          <t>/api/v1/hierarchy/nodes/{id}/children</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>address→노드 해석</t>
+          <t>하위 노드 조회</t>
         </is>
       </c>
     </row>
@@ -3363,17 +3363,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}</t>
+          <t>/api/v1/hierarchy/nodes</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>노드 개명·속성 수정 (승인 대상)</t>
+          <t>노드 생성 (승인 대상)</t>
         </is>
       </c>
     </row>
@@ -3388,17 +3388,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}</t>
+          <t>/api/v1/hierarchy/nodes/{id}/move</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>노드 삭제 — DB 상호관계 점검 후</t>
+          <t>노드 이동 — Address 추적</t>
         </is>
       </c>
     </row>
@@ -3408,22 +3408,22 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/groups</t>
+          <t>/api/v1/hierarchy/resolve</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>코드 그룹 등록</t>
+          <t>address→노드 해석</t>
         </is>
       </c>
     </row>
@@ -3433,22 +3433,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products</t>
+          <t>/api/v1/hierarchy/search</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Product Code 등록</t>
+          <t>이름·비고·심볼 통합 검색 (M-15-6)</t>
         </is>
       </c>
     </row>
@@ -3458,22 +3458,22 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products/{id}/check-duplicate</t>
+          <t>/api/v1/hierarchy/nodes/{id}</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Main Code 중복검토</t>
+          <t>노드 개명·속성 수정 (승인 대상)</t>
         </is>
       </c>
     </row>
@@ -3483,22 +3483,22 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/relationships</t>
+          <t>/api/v1/hierarchy/nodes/{id}</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Mother-Child 관계 등록</t>
+          <t>노드 삭제 — DB 상호관계 점검 후</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products/{id}/expand</t>
+          <t>/api/v1/codes/groups</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>BOM 전개</t>
+          <t>코드 그룹 등록</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/relationships/running-test</t>
+          <t>/api/v1/codes/products</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Part List Running Test</t>
+          <t>Product Code 등록</t>
         </is>
       </c>
     </row>
@@ -3563,17 +3563,17 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/arrangements</t>
+          <t>/api/v1/codes/products/{id}/check-duplicate</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Arrangement 등록</t>
+          <t>Main Code 중복검토</t>
         </is>
       </c>
     </row>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/values/import-excel</t>
+          <t>/api/v1/codes/relationships</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>코드 값 Excel Import (CODE-016)</t>
+          <t>Mother-Child 관계 등록</t>
         </is>
       </c>
     </row>
@@ -3613,17 +3613,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/groups/{id}/export-excel</t>
+          <t>/api/v1/codes/products/{id}/expand</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Registered Code Table Export (CODE-016)</t>
+          <t>BOM 전개</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings</t>
+          <t>/api/v1/codes/relationships/running-test</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>도면 등록</t>
+          <t>Part List Running Test</t>
         </is>
       </c>
     </row>
@@ -3658,22 +3658,22 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/codes/arrangements</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 조회 (block 파라미터)</t>
+          <t>Arrangement 등록</t>
         </is>
       </c>
     </row>
@@ -3683,22 +3683,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/codes/values/import-excel</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 저장</t>
+          <t>코드 값 Excel Import (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/revisions</t>
+          <t>/api/v1/codes/groups/{id}/export-excel</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>개정 생성</t>
+          <t>Registered Code Table Export (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3743,12 +3743,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/dimensions</t>
+          <t>/api/v1/drawings</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>치수 등록 (Macro 바인딩)</t>
+          <t>도면 등록</t>
         </is>
       </c>
     </row>
@@ -3763,17 +3763,17 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/relations</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>부품 관계 등록</t>
+          <t>DrawingDocument 조회 (block 파라미터)</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/import</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>DXF/DWG/PDF/STEP Import</t>
+          <t>DrawingDocument 저장</t>
         </is>
       </c>
     </row>
@@ -3818,12 +3818,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/export</t>
+          <t>/api/v1/drawings/{id}/revisions</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>DXF/PDF Export</t>
+          <t>개정 생성</t>
         </is>
       </c>
     </row>
@@ -3838,17 +3838,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/referencers</t>
+          <t>/api/v1/drawings/{id}/dimensions</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Where-used 역참조 조회 (DWG-026)</t>
+          <t>치수 등록 (Macro 바인딩)</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/variants</t>
+          <t>/api/v1/drawings/{id}/relations</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Variants 목록 (DWG-027)</t>
+          <t>부품 관계 등록</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/supersede</t>
+          <t>/api/v1/drawings/import</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>대체 관계 등록 — old→new (DWG-027)</t>
+          <t>DXF/DWG/PDF/STEP Import</t>
         </is>
       </c>
     </row>
@@ -3913,17 +3913,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/dimensions/{dimId}</t>
+          <t>/api/v1/drawings/{id}/export</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>치수 Macro/Variant 바인딩 수정 (XOR 검증)</t>
+          <t>DXF/PDF Export</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/parts</t>
+          <t>/api/v1/drawings/{id}/referencers</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>부품 마스터 목록·검색 (DWG-017)</t>
+          <t>Where-used 역참조 조회 (DWG-026)</t>
         </is>
       </c>
     </row>
@@ -3963,17 +3963,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/parts</t>
+          <t>/api/v1/drawings/{id}/variants</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>부품 등록</t>
+          <t>Variants 목록 (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/materials</t>
+          <t>/api/v1/drawings/{id}/supersede</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>재질 등록 — hazard_class 포함 (DWG-018)</t>
+          <t>대체 관계 등록 — old→new (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -4008,22 +4008,22 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables</t>
+          <t>/api/v1/drawings/{id}/dimensions/{dimId}</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Table 정의 생성</t>
+          <t>치수 Macro/Variant 바인딩 수정 (XOR 검증)</t>
         </is>
       </c>
     </row>
@@ -4033,22 +4033,22 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/rows:bulk</t>
+          <t>/api/v1/parts</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>행 일괄 입력</t>
+          <t>부품 마스터 목록·검색 (DWG-017)</t>
         </is>
       </c>
     </row>
@@ -4058,22 +4058,22 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/query</t>
+          <t>/api/v1/parts</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>범위 조회 (Macro 참조용)</t>
+          <t>부품 등록</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/import-excel</t>
+          <t>/api/v1/materials</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Excel Import</t>
+          <t>재질 등록 — hazard_class 포함 (DWG-018)</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms</t>
+          <t>/api/v1/tables</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>UI Form 저장</t>
+          <t>Table 정의 생성</t>
         </is>
       </c>
     </row>
@@ -4133,22 +4133,22 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}</t>
+          <t>/api/v1/tables/{id}/rows:bulk</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Form 렌더 정의 조회</t>
+          <t>행 일괄 입력</t>
         </is>
       </c>
     </row>
@@ -4158,22 +4158,22 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}/publish</t>
+          <t>/api/v1/tables/{id}/query</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Form 게시 (승인 후)</t>
+          <t>범위 조회 (Macro 참조용)</t>
         </is>
       </c>
     </row>
@@ -4183,22 +4183,22 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/templets</t>
+          <t>/api/v1/tables/import-excel</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Templet 목록</t>
+          <t>Excel Import</t>
         </is>
       </c>
     </row>
@@ -4208,22 +4208,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections</t>
+          <t>/api/v1/toolbox/forms</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>선정 세션 목록 (project·상태 필터)</t>
+          <t>UI Form 저장</t>
         </is>
       </c>
     </row>
@@ -4233,22 +4233,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections</t>
+          <t>/api/v1/toolbox/forms/{id}</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>선정 세션 생성</t>
+          <t>Form 렌더 정의 조회</t>
         </is>
       </c>
     </row>
@@ -4258,22 +4258,22 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/slots</t>
+          <t>/api/v1/toolbox/forms/{id}/publish</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Slot 값 선택</t>
+          <t>Form 게시 (승인 후)</t>
         </is>
       </c>
     </row>
@@ -4283,22 +4283,22 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/finalize</t>
+          <t>/api/v1/toolbox/templets</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>완성품 Code 확정</t>
+          <t>Templet 목록</t>
         </is>
       </c>
     </row>
@@ -4308,22 +4308,22 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
+          <t>/api/v1/toolbox/forms/{id}</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>비규격 검토 요청</t>
+          <t>DRAFT Form 삭제 (게시본 불가)</t>
         </is>
       </c>
     </row>
@@ -4338,17 +4338,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/runs</t>
+          <t>/api/v1/cpq/selections</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run 실행 요청</t>
+          <t>선정 세션 목록 (project·상태 필터)</t>
         </is>
       </c>
     </row>
@@ -4363,17 +4363,17 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}</t>
+          <t>/api/v1/cpq/selections</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Run 상태 조회</t>
+          <t>선정 세션 생성</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}/outputs</t>
+          <t>/api/v1/cpq/selections/{id}/slots</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>산출물 목록</t>
+          <t>Slot 값 선택</t>
         </is>
       </c>
     </row>
@@ -4413,17 +4413,17 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}/bom/export</t>
+          <t>/api/v1/cpq/selections/{id}/finalize</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>BOM Excel Export (RUN-010)</t>
+          <t>완성품 Code 확정</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices</t>
+          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>단가 등록</t>
+          <t>비규격 검토 요청</t>
         </is>
       </c>
     </row>
@@ -4458,22 +4458,22 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices/resolve</t>
+          <t>/api/v1/cpq/selections/{id}/runs</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>적용 단가 해석 (source 우선순위)</t>
+          <t>EDIM Run 실행 요청</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4483,22 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/pcr</t>
+          <t>/api/v1/cpq/runs/{runId}</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>PCR 생성</t>
+          <t>Run 상태 조회</t>
         </is>
       </c>
     </row>
@@ -4508,22 +4508,22 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations</t>
+          <t>/api/v1/cpq/runs/{runId}/outputs</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>견적서 생성</t>
+          <t>산출물 목록</t>
         </is>
       </c>
     </row>
@@ -4533,22 +4533,22 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations/{id}/render</t>
+          <t>/api/v1/cpq/runs/{runId}/bom/export</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>견적서 PDF 출력</t>
+          <t>BOM Excel Export (RUN-010)</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/projects</t>
+          <t>/api/v1/cost/prices</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Project 등록 PS — 채번 (ERP-001)</t>
+          <t>단가 등록</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/projects</t>
+          <t>/api/v1/cost/prices/resolve</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Project 목록 — 영업단계 필터</t>
+          <t>적용 단가 해석 (source 우선순위)</t>
         </is>
       </c>
     </row>
@@ -4608,22 +4608,22 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/processes</t>
+          <t>/api/v1/cost/pcr</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>프로세스 정의 목록</t>
+          <t>PCR 생성</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/process-defs</t>
+          <t>/api/v1/cost/quotations</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>프로세스 정의 생성 (W-14, ADMIN — 코드 신설은 Platform)</t>
+          <t>견적서 생성</t>
         </is>
       </c>
     </row>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/process-defs/{id}</t>
+          <t>/api/v1/cost/quotations/{id}/render</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>정의 수정 — 선행/후행(edge)·기한·Form</t>
+          <t>견적서 PDF 출력</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events</t>
+          <t>/api/v1/projects</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>프로세스 이벤트 생성</t>
+          <t>Project 등록 PS — 채번 (ERP-001)</t>
         </is>
       </c>
     </row>
@@ -4713,17 +4713,17 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events/{id}/status</t>
+          <t>/api/v1/projects</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>이벤트 상태 전이</t>
+          <t>Project 목록 — 영업단계 필터</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4743,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events</t>
+          <t>/api/v1/erp/processes</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>업무함 (assignee/status 필터)</t>
+          <t>프로세스 정의 목록</t>
         </is>
       </c>
     </row>
@@ -4763,17 +4763,17 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/dashboard/project/{projectId}</t>
+          <t>/api/v1/erp/process-defs</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 Dashboard 집계</t>
+          <t>프로세스 정의 생성 (W-14, ADMIN — 코드 신설은 Platform)</t>
         </is>
       </c>
     </row>
@@ -4788,17 +4788,17 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/work-processes</t>
+          <t>/api/v1/erp/process-defs/{id}</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Work Process 공정 데이터 등록</t>
+          <t>정의 수정 — 선행/후행(edge)·기한·Form</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/supplier-code-maps</t>
+          <t>/api/v1/erp/events</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>사용자↔공급자 코드 매핑 (ERP-018)</t>
+          <t>프로세스 이벤트 생성</t>
         </is>
       </c>
     </row>
@@ -4833,22 +4833,22 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals</t>
+          <t>/api/v1/erp/events/{id}/status</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>승인 요청 생성</t>
+          <t>이벤트 상태 전이</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/inbox</t>
+          <t>/api/v1/erp/events</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>승인함</t>
+          <t>업무함 (assignee/status 필터)</t>
         </is>
       </c>
     </row>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/{id}/decide</t>
+          <t>/api/v1/erp/dashboard</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>승인/반려 결정</t>
+          <t>전사 Dashboard — 부서별 Event·이상 경고 (W-10)</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/history</t>
+          <t>/api/v1/erp/dashboard/project/{projectId}</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>승인 이력</t>
+          <t>프로젝트 Dashboard 집계</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/render</t>
+          <t>/api/v1/erp/work-processes</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Print Form + 데이터 → PDF</t>
+          <t>Work Process 공정 데이터 등록</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/export-office</t>
+          <t>/api/v1/erp/supplier-code-maps</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>xlsx/docx 내보내기</t>
+          <t>사용자↔공급자 코드 매핑 (ERP-018)</t>
         </is>
       </c>
     </row>
@@ -4983,22 +4983,22 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls</t>
+          <t>/api/v1/approvals</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>문서함 목록 — Released Status·Grade 필터 (DOC-001)</t>
+          <t>승인 요청 생성</t>
         </is>
       </c>
     </row>
@@ -5008,22 +5008,22 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls/{id}/status</t>
+          <t>/api/v1/approvals/inbox</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Released Status 전이 — Set-up→Check→Approve→Accepted</t>
+          <t>승인함</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls/allocate-code</t>
+          <t>/api/v1/approvals/{id}/decide</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Document Code 채번 (DOC-003)</t>
+          <t>승인/반려 결정</t>
         </is>
       </c>
     </row>
@@ -5058,22 +5058,22 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/upload-url</t>
+          <t>/api/v1/approvals/history</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>업로드 서명 URL</t>
+          <t>승인 이력</t>
         </is>
       </c>
     </row>
@@ -5083,22 +5083,22 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/{id}/download-url</t>
+          <t>/api/v1/documents/render</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>다운로드 서명 URL</t>
+          <t>Print Form + 데이터 → PDF</t>
         </is>
       </c>
     </row>
@@ -5108,22 +5108,22 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files</t>
+          <t>/api/v1/documents/export-office</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Project Folder 파일 목록</t>
+          <t>xlsx/docx 내보내기</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications</t>
+          <t>/api/v1/doc-controls</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>알림 목록</t>
+          <t>문서함 목록 — Released Status·Grade 필터 (DOC-001)</t>
         </is>
       </c>
     </row>
@@ -5158,22 +5158,22 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications/read</t>
+          <t>/api/v1/doc-controls/{id}/status</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>읽음 처리</t>
+          <t>Released Status 전이 — Set-up→Check→Approve→Accepted</t>
         </is>
       </c>
     </row>
@@ -5183,22 +5183,22 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>/ws/notifications</t>
+          <t>/api/v1/doc-controls/allocate-code</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>실시간 알림 채널</t>
+          <t>Document Code 채번 (DOC-003)</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>ENG-01 Macro</t>
+          <t>SVC-12 File</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros/{id}/test-run</t>
+          <t>/api/v1/files/upload-url</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Macro Test Run (조건값→결과)</t>
+          <t>업로드 서명 URL</t>
         </is>
       </c>
     </row>
@@ -5233,22 +5233,22 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-12 File</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/generate</t>
+          <t>/api/v1/files/{id}/download-url</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Prompt→Macro 생성</t>
+          <t>다운로드 서명 URL</t>
         </is>
       </c>
     </row>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-12 File</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/convert</t>
+          <t>/api/v1/files</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>표현 간 변환 (from/to)</t>
+          <t>Project Folder 파일 목록</t>
         </is>
       </c>
     </row>
@@ -5283,22 +5283,22 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-13 Notify</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/ui/suggest</t>
+          <t>/api/v1/notifications</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>UI Form 초안 제안</t>
+          <t>알림 목록</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-13 Notify</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/chat</t>
+          <t>/api/v1/notifications/read</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>읽음 처리</t>
         </is>
       </c>
     </row>
@@ -5333,22 +5333,22 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SVC-13 Notify</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/learning/jobs</t>
+          <t>/ws/notifications</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>학습 잡 실행 (Platform 전용)</t>
+          <t>실시간 알림 채널</t>
         </is>
       </c>
     </row>
@@ -5358,22 +5358,22 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>INT-05 QR</t>
+          <t>ENG-01 Macro</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/qr/issue</t>
+          <t>/api/v1/macros</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>도면·서류·Project·자산 QR 발급 (APP-001)</t>
+          <t>Macro 목록·검색 (v0.4 — CRUD 부재 결함 수정)</t>
         </is>
       </c>
     </row>
@@ -5383,27 +5383,302 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
+          <t>ENG-01 Macro</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/macros</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Macro 생성 — 4표현 저장, 참조 추출·DAG 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>ENG-01 Macro</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/macros/{id}</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Macro 상세 (버전 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>ENG-01 Macro</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/macros/{id}</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Macro 수정 — 새 버전 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>ENG-01 Macro</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/macros/{id}</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>DRAFT Macro 삭제 (승인본 삭제 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>ENG-01 Macro</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/macros/{id}/test-run</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Macro Test Run (조건값→결과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/macro/generate</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Prompt→Macro 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/macro/convert</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>표현 간 변환 (from/to)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/ui/suggest</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>UI Form 초안 제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/chat</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>사내 자료 챗봇</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/learning/jobs</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>학습 잡 실행 (Platform 전용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
           <t>INT-05 QR</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/qr/issue</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>도면·서류·Project·자산 QR 발급 (APP-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>INT-05 QR</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>/api/v1/qr/resolve</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>QR 해석 → 대상 링크·권한 검사</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E96"/>
+  <autoFilter ref="A1:E107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -2627,12 +2627,16 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>구축완료</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>PostgreSQL 16 컨테이너(edim-postgres, 127.0.0.1:5432) — EDIM 스키마 53테이블 적용·검증됨</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">

--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컴포넌트목록'!$A$1:$L$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API목록'!$A$1:$E$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -632,7 +632,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>106개 (대표 엔드포인트 — 상세 스펙은 OpenAPI 원천, 개발표준 §3)</t>
+          <t>108개 (대표 엔드포인트 — 상세 스펙은 OpenAPI 원천, 개발표준 §3)</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/auth/permissions</t>
+          <t>/api/v1/i18n/{locale}</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>리소스별 권한 조회</t>
+          <t>데이터 라벨 번역 번들 (ko/en/ja/zh, KO 폴백) — SYS-021</t>
         </is>
       </c>
     </row>
@@ -3167,17 +3167,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/i18n/translations</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>사용자 목록 (부서·상태 필터, ADMIN)</t>
+          <t>번역 등록·수정 (ADMIN, 일괄 Import 지원)</t>
         </is>
       </c>
     </row>
@@ -3192,17 +3192,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/auth/permissions</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>사용자 등록 (SYS-003)</t>
+          <t>리소스별 권한 조회</t>
         </is>
       </c>
     </row>
@@ -3217,17 +3217,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/users/{id}</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>사용자 수정·상태 변경 (ACTIVE/LOCKED/RETIRED)</t>
+          <t>사용자 목록 (부서·상태 필터, ADMIN)</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/roles</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>역할 생성·권한 부여 (SYS-004/005)</t>
+          <t>사용자 등록 (SYS-003)</t>
         </is>
       </c>
     </row>
@@ -3267,17 +3267,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tenants</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>테넌트 목록·상태 (Platform 전용)</t>
+          <t>사용자 수정·상태 변경 (ACTIVE/LOCKED/RETIRED)</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tenants</t>
+          <t>/api/v1/roles</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>테넌트 생성 — sys_tenant (ADM-001, Platform 전용)</t>
+          <t>역할 생성·권한 부여 (SYS-004/005)</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/trees</t>
+          <t>/api/v1/tenants</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Tree 목록 (type 필터)</t>
+          <t>테넌트 목록·상태 (Platform 전용)</t>
         </is>
       </c>
     </row>
@@ -3337,22 +3337,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>SVC-02 Hierarchy</t>
+          <t>SVC-01 Auth</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}/children</t>
+          <t>/api/v1/tenants</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>하위 노드 조회</t>
+          <t>테넌트 생성 — sys_tenant (ADM-001, Platform 전용)</t>
         </is>
       </c>
     </row>
@@ -3367,17 +3367,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes</t>
+          <t>/api/v1/hierarchy/trees</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>노드 생성 (승인 대상)</t>
+          <t>Tree 목록 (type 필터)</t>
         </is>
       </c>
     </row>
@@ -3392,17 +3392,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}/move</t>
+          <t>/api/v1/hierarchy/nodes/{id}/children</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>노드 이동 — Address 추적</t>
+          <t>하위 노드 조회</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/resolve</t>
+          <t>/api/v1/hierarchy/nodes</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>address→노드 해석</t>
+          <t>노드 생성 (승인 대상)</t>
         </is>
       </c>
     </row>
@@ -3442,17 +3442,17 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/search</t>
+          <t>/api/v1/hierarchy/nodes/{id}/move</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>이름·비고·심볼 통합 검색 (M-15-6)</t>
+          <t>노드 이동 — Address 추적</t>
         </is>
       </c>
     </row>
@@ -3467,17 +3467,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}</t>
+          <t>/api/v1/hierarchy/resolve</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>노드 개명·속성 수정 (승인 대상)</t>
+          <t>address→노드 해석</t>
         </is>
       </c>
     </row>
@@ -3492,17 +3492,17 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/hierarchy/nodes/{id}</t>
+          <t>/api/v1/hierarchy/search</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>노드 삭제 — DB 상호관계 점검 후</t>
+          <t>이름·비고·심볼 통합 검색 (M-15-6)</t>
         </is>
       </c>
     </row>
@@ -3512,22 +3512,22 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/groups</t>
+          <t>/api/v1/hierarchy/nodes/{id}</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>코드 그룹 등록</t>
+          <t>노드 개명·속성 수정 (승인 대상)</t>
         </is>
       </c>
     </row>
@@ -3537,22 +3537,22 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>SVC-03 Code</t>
+          <t>SVC-02 Hierarchy</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products</t>
+          <t>/api/v1/hierarchy/nodes/{id}</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Product Code 등록</t>
+          <t>노드 삭제 — DB 상호관계 점검 후</t>
         </is>
       </c>
     </row>
@@ -3567,17 +3567,17 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products/{id}/check-duplicate</t>
+          <t>/api/v1/codes/groups</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Main Code 중복검토</t>
+          <t>코드 그룹 등록</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/relationships</t>
+          <t>/api/v1/codes/products</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Mother-Child 관계 등록</t>
+          <t>Product Code 등록</t>
         </is>
       </c>
     </row>
@@ -3617,17 +3617,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/products/{id}/expand</t>
+          <t>/api/v1/codes/products/{id}/check-duplicate</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>BOM 전개</t>
+          <t>Main Code 중복검토</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3647,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/relationships/running-test</t>
+          <t>/api/v1/codes/relationships</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Part List Running Test</t>
+          <t>Mother-Child 관계 등록</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/arrangements</t>
+          <t>/api/v1/codes/products/{id}/expand</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Arrangement 등록</t>
+          <t>BOM 전개</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/values/import-excel</t>
+          <t>/api/v1/codes/relationships/running-test</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>코드 값 Excel Import (CODE-016)</t>
+          <t>Part List Running Test</t>
         </is>
       </c>
     </row>
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/codes/groups/{id}/export-excel</t>
+          <t>/api/v1/codes/arrangements</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Registered Code Table Export (CODE-016)</t>
+          <t>Arrangement 등록</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings</t>
+          <t>/api/v1/codes/values/import-excel</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>도면 등록</t>
+          <t>코드 값 Excel Import (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>SVC-04 Drawing</t>
+          <t>SVC-03 Code</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/codes/groups/{id}/export-excel</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 조회 (block 파라미터)</t>
+          <t>Registered Code Table Export (CODE-016)</t>
         </is>
       </c>
     </row>
@@ -3792,17 +3792,17 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/document</t>
+          <t>/api/v1/drawings</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>DrawingDocument 저장</t>
+          <t>도면 등록</t>
         </is>
       </c>
     </row>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/revisions</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>개정 생성</t>
+          <t>DrawingDocument 조회 (block 파라미터)</t>
         </is>
       </c>
     </row>
@@ -3842,17 +3842,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/dimensions</t>
+          <t>/api/v1/drawings/{id}/document</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>치수 등록 (Macro 바인딩)</t>
+          <t>DrawingDocument 저장</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/relations</t>
+          <t>/api/v1/drawings/{id}/revisions</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>부품 관계 등록</t>
+          <t>개정 생성</t>
         </is>
       </c>
     </row>
@@ -3897,12 +3897,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/import</t>
+          <t>/api/v1/drawings/{id}/dimensions</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>DXF/DWG/PDF/STEP Import</t>
+          <t>치수 등록 (Macro 바인딩)</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/export</t>
+          <t>/api/v1/drawings/{id}/relations</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>DXF/PDF Export</t>
+          <t>부품 관계 등록</t>
         </is>
       </c>
     </row>
@@ -3942,17 +3942,17 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/referencers</t>
+          <t>/api/v1/drawings/import</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Where-used 역참조 조회 (DWG-026)</t>
+          <t>DXF/DWG/PDF/STEP Import</t>
         </is>
       </c>
     </row>
@@ -3967,17 +3967,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/variants</t>
+          <t>/api/v1/drawings/{id}/export</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Variants 목록 (DWG-027)</t>
+          <t>DXF/PDF Export</t>
         </is>
       </c>
     </row>
@@ -3992,17 +3992,17 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/supersede</t>
+          <t>/api/v1/drawings/{id}/referencers</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>대체 관계 등록 — old→new (DWG-027)</t>
+          <t>Where-used 역참조 조회 (DWG-026)</t>
         </is>
       </c>
     </row>
@@ -4017,17 +4017,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/drawings/{id}/dimensions/{dimId}</t>
+          <t>/api/v1/drawings/{id}/variants</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>치수 Macro/Variant 바인딩 수정 (XOR 검증)</t>
+          <t>Variants 목록 (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -4042,17 +4042,17 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/parts</t>
+          <t>/api/v1/drawings/{id}/supersede</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>부품 마스터 목록·검색 (DWG-017)</t>
+          <t>대체 관계 등록 — old→new (DWG-027)</t>
         </is>
       </c>
     </row>
@@ -4067,17 +4067,17 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/parts</t>
+          <t>/api/v1/drawings/{id}/dimensions/{dimId}</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>부품 등록</t>
+          <t>치수 Macro/Variant 바인딩 수정 (XOR 검증)</t>
         </is>
       </c>
     </row>
@@ -4092,17 +4092,17 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/materials</t>
+          <t>/api/v1/parts</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>재질 등록 — hazard_class 포함 (DWG-018)</t>
+          <t>부품 마스터 목록·검색 (DWG-017)</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables</t>
+          <t>/api/v1/parts</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Table 정의 생성</t>
+          <t>부품 등록</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>SVC-05 Table</t>
+          <t>SVC-04 Drawing</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/rows:bulk</t>
+          <t>/api/v1/materials</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>행 일괄 입력</t>
+          <t>재질 등록 — hazard_class 포함 (DWG-018)</t>
         </is>
       </c>
     </row>
@@ -4167,17 +4167,17 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/{id}/query</t>
+          <t>/api/v1/tables</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>범위 조회 (Macro 참조용)</t>
+          <t>Table 정의 생성</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/tables/import-excel</t>
+          <t>/api/v1/tables/{id}/rows:bulk</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Excel Import</t>
+          <t>행 일괄 입력</t>
         </is>
       </c>
     </row>
@@ -4212,22 +4212,22 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms</t>
+          <t>/api/v1/tables/{id}/query</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>UI Form 저장</t>
+          <t>범위 조회 (Macro 참조용)</t>
         </is>
       </c>
     </row>
@@ -4237,22 +4237,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>SVC-06 Toolbox</t>
+          <t>SVC-05 Table</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}</t>
+          <t>/api/v1/tables/import-excel</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Form 렌더 정의 조회</t>
+          <t>Excel Import</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}/publish</t>
+          <t>/api/v1/toolbox/forms</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Form 게시 (승인 후)</t>
+          <t>UI Form 저장</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4297,12 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/templets</t>
+          <t>/api/v1/toolbox/forms/{id}</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Templet 목록</t>
+          <t>Form 렌더 정의 조회</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4317,17 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/toolbox/forms/{id}</t>
+          <t>/api/v1/toolbox/forms/{id}/publish</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>DRAFT Form 삭제 (게시본 불가)</t>
+          <t>Form 게시 (승인 후)</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections</t>
+          <t>/api/v1/toolbox/templets</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>선정 세션 목록 (project·상태 필터)</t>
+          <t>Templet 목록</t>
         </is>
       </c>
     </row>
@@ -4362,22 +4362,22 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>SVC-07 CPQ</t>
+          <t>SVC-06 Toolbox</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections</t>
+          <t>/api/v1/toolbox/forms/{id}</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>선정 세션 생성</t>
+          <t>DRAFT Form 삭제 (게시본 불가)</t>
         </is>
       </c>
     </row>
@@ -4392,17 +4392,17 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/slots</t>
+          <t>/api/v1/cpq/selections</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Slot 값 선택</t>
+          <t>선정 세션 목록 (project·상태 필터)</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4422,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/finalize</t>
+          <t>/api/v1/cpq/selections</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>완성품 Code 확정</t>
+          <t>선정 세션 생성</t>
         </is>
       </c>
     </row>
@@ -4442,17 +4442,17 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
+          <t>/api/v1/cpq/selections/{id}/slots</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>비규격 검토 요청</t>
+          <t>Slot 값 선택</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/selections/{id}/runs</t>
+          <t>/api/v1/cpq/selections/{id}/finalize</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run 실행 요청</t>
+          <t>완성품 Code 확정</t>
         </is>
       </c>
     </row>
@@ -4492,17 +4492,17 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}</t>
+          <t>/api/v1/cpq/selections/{id}/x-code-review</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Run 상태 조회</t>
+          <t>비규격 검토 요청</t>
         </is>
       </c>
     </row>
@@ -4517,17 +4517,17 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}/outputs</t>
+          <t>/api/v1/cpq/selections/{id}/runs</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>산출물 목록</t>
+          <t>EDIM Run 실행 요청</t>
         </is>
       </c>
     </row>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cpq/runs/{runId}/bom/export</t>
+          <t>/api/v1/cpq/runs/{runId}</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>BOM Excel Export (RUN-010)</t>
+          <t>Run 상태 조회</t>
         </is>
       </c>
     </row>
@@ -4562,22 +4562,22 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices</t>
+          <t>/api/v1/cpq/runs/{runId}/outputs</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>단가 등록</t>
+          <t>산출물 목록</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>SVC-08 Cost</t>
+          <t>SVC-07 CPQ</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/prices/resolve</t>
+          <t>/api/v1/cpq/runs/{runId}/bom/export</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>적용 단가 해석 (source 우선순위)</t>
+          <t>BOM Excel Export (RUN-010)</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/pcr</t>
+          <t>/api/v1/cost/prices</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>PCR 생성</t>
+          <t>단가 등록</t>
         </is>
       </c>
     </row>
@@ -4642,17 +4642,17 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations</t>
+          <t>/api/v1/cost/prices/resolve</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>견적서 생성</t>
+          <t>적용 단가 해석 (source 우선순위)</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4672,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/cost/quotations/{id}/render</t>
+          <t>/api/v1/cost/pcr</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>견적서 PDF 출력</t>
+          <t>PCR 생성</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/projects</t>
+          <t>/api/v1/cost/quotations</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Project 등록 PS — 채번 (ERP-001)</t>
+          <t>견적서 생성</t>
         </is>
       </c>
     </row>
@@ -4712,22 +4712,22 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>SVC-09 ERP</t>
+          <t>SVC-08 Cost</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/projects</t>
+          <t>/api/v1/cost/quotations/{id}/render</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Project 목록 — 영업단계 필터</t>
+          <t>견적서 PDF 출력</t>
         </is>
       </c>
     </row>
@@ -4742,17 +4742,17 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/processes</t>
+          <t>/api/v1/projects</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>프로세스 정의 목록</t>
+          <t>Project 등록 PS — 채번 (ERP-001)</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/process-defs</t>
+          <t>/api/v1/projects</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>프로세스 정의 생성 (W-14, ADMIN — 코드 신설은 Platform)</t>
+          <t>Project 목록 — 영업단계 필터</t>
         </is>
       </c>
     </row>
@@ -4792,17 +4792,17 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/process-defs/{id}</t>
+          <t>/api/v1/erp/processes</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>정의 수정 — 선행/후행(edge)·기한·Form</t>
+          <t>프로세스 정의 목록</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events</t>
+          <t>/api/v1/erp/process-defs</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>프로세스 이벤트 생성</t>
+          <t>프로세스 정의 생성 (W-14, ADMIN — 코드 신설은 Platform)</t>
         </is>
       </c>
     </row>
@@ -4847,12 +4847,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/events/{id}/status</t>
+          <t>/api/v1/erp/process-defs/{id}</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>이벤트 상태 전이</t>
+          <t>정의 수정 — 선행/후행(edge)·기한·Form</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>업무함 (assignee/status 필터)</t>
+          <t>프로세스 이벤트 생성</t>
         </is>
       </c>
     </row>
@@ -4892,17 +4892,17 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/dashboard</t>
+          <t>/api/v1/erp/events/{id}/status</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>전사 Dashboard — 부서별 Event·이상 경고 (W-10)</t>
+          <t>이벤트 상태 전이</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/dashboard/project/{projectId}</t>
+          <t>/api/v1/erp/events</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 Dashboard 집계</t>
+          <t>업무함 (assignee/status 필터)</t>
         </is>
       </c>
     </row>
@@ -4942,17 +4942,17 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/work-processes</t>
+          <t>/api/v1/erp/dashboard</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Work Process 공정 데이터 등록</t>
+          <t>전사 Dashboard — 부서별 Event·이상 경고 (W-10)</t>
         </is>
       </c>
     </row>
@@ -4967,17 +4967,17 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/erp/supplier-code-maps</t>
+          <t>/api/v1/erp/dashboard/project/{projectId}</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>사용자↔공급자 코드 매핑 (ERP-018)</t>
+          <t>프로젝트 Dashboard 집계</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals</t>
+          <t>/api/v1/erp/work-processes</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>승인 요청 생성</t>
+          <t>Work Process 공정 데이터 등록</t>
         </is>
       </c>
     </row>
@@ -5012,22 +5012,22 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>SVC-10 Approval</t>
+          <t>SVC-09 ERP</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/inbox</t>
+          <t>/api/v1/erp/supplier-code-maps</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>승인함</t>
+          <t>사용자↔공급자 코드 매핑 (ERP-018)</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/{id}/decide</t>
+          <t>/api/v1/approvals</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>승인/반려 결정</t>
+          <t>승인 요청 생성</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/approvals/history</t>
+          <t>/api/v1/approvals/inbox</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>승인 이력</t>
+          <t>승인함</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/render</t>
+          <t>/api/v1/approvals/{id}/decide</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>Print Form + 데이터 → PDF</t>
+          <t>승인/반려 결정</t>
         </is>
       </c>
     </row>
@@ -5112,22 +5112,22 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>SVC-11 Print</t>
+          <t>SVC-10 Approval</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/documents/export-office</t>
+          <t>/api/v1/approvals/history</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>xlsx/docx 내보내기</t>
+          <t>승인 이력</t>
         </is>
       </c>
     </row>
@@ -5142,17 +5142,17 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls</t>
+          <t>/api/v1/documents/render</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>문서함 목록 — Released Status·Grade 필터 (DOC-001)</t>
+          <t>Print Form + 데이터 → PDF</t>
         </is>
       </c>
     </row>
@@ -5167,17 +5167,17 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls/{id}/status</t>
+          <t>/api/v1/documents/export-office</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Released Status 전이 — Set-up→Check→Approve→Accepted</t>
+          <t>xlsx/docx 내보내기</t>
         </is>
       </c>
     </row>
@@ -5192,17 +5192,17 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/doc-controls/allocate-code</t>
+          <t>/api/v1/doc-controls</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Document Code 채번 (DOC-003)</t>
+          <t>문서함 목록 — Released Status·Grade 필터 (DOC-001)</t>
         </is>
       </c>
     </row>
@@ -5212,22 +5212,22 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/upload-url</t>
+          <t>/api/v1/doc-controls/{id}/status</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>업로드 서명 URL</t>
+          <t>Released Status 전이 — Set-up→Check→Approve→Accepted</t>
         </is>
       </c>
     </row>
@@ -5237,22 +5237,22 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>SVC-12 File</t>
+          <t>SVC-11 Print</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files/{id}/download-url</t>
+          <t>/api/v1/doc-controls/allocate-code</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>다운로드 서명 URL</t>
+          <t>Document Code 채번 (DOC-003)</t>
         </is>
       </c>
     </row>
@@ -5267,17 +5267,17 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/files</t>
+          <t>/api/v1/files/upload-url</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Project Folder 파일 목록</t>
+          <t>업로드 서명 URL</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-12 File</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications</t>
+          <t>/api/v1/files/{id}/download-url</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>알림 목록</t>
+          <t>다운로드 서명 URL</t>
         </is>
       </c>
     </row>
@@ -5312,22 +5312,22 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>SVC-13 Notify</t>
+          <t>SVC-12 File</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/notifications/read</t>
+          <t>/api/v1/files</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>읽음 처리</t>
+          <t>Project Folder 파일 목록</t>
         </is>
       </c>
     </row>
@@ -5342,17 +5342,17 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>/ws/notifications</t>
+          <t>/api/v1/notifications</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>실시간 알림 채널</t>
+          <t>알림 목록</t>
         </is>
       </c>
     </row>
@@ -5362,22 +5362,22 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>ENG-01 Macro</t>
+          <t>SVC-13 Notify</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros</t>
+          <t>/api/v1/notifications/read</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Macro 목록·검색 (v0.4 — CRUD 부재 결함 수정)</t>
+          <t>읽음 처리</t>
         </is>
       </c>
     </row>
@@ -5387,22 +5387,22 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>ENG-01 Macro</t>
+          <t>SVC-13 Notify</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros</t>
+          <t>/ws/notifications</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Macro 생성 — 4표현 저장, 참조 추출·DAG 검증</t>
+          <t>실시간 알림 채널</t>
         </is>
       </c>
     </row>
@@ -5422,12 +5422,12 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros/{id}</t>
+          <t>/api/v1/macros</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Macro 상세 (버전 포함)</t>
+          <t>Macro 목록·검색 (v0.4 — CRUD 부재 결함 수정)</t>
         </is>
       </c>
     </row>
@@ -5442,17 +5442,17 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros/{id}</t>
+          <t>/api/v1/macros</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Macro 수정 — 새 버전 생성</t>
+          <t>Macro 생성 — 4표현 저장, 참조 추출·DAG 검증</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>DRAFT Macro 삭제 (승인본 삭제 불가)</t>
+          <t>Macro 상세 (버전 포함)</t>
         </is>
       </c>
     </row>
@@ -5492,17 +5492,17 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/macros/{id}/test-run</t>
+          <t>/api/v1/macros/{id}</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Macro Test Run (조건값→결과)</t>
+          <t>Macro 수정 — 새 버전 생성</t>
         </is>
       </c>
     </row>
@@ -5512,22 +5512,22 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ENG-01 Macro</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/generate</t>
+          <t>/api/v1/macros/{id}</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Prompt→Macro 생성</t>
+          <t>DRAFT Macro 삭제 (승인본 삭제 불가)</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ENG-01 Macro</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/macro/convert</t>
+          <t>/api/v1/macros/{id}/test-run</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>표현 간 변환 (from/to)</t>
+          <t>Macro Test Run (조건값→결과)</t>
         </is>
       </c>
     </row>
@@ -5572,12 +5572,12 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/ui/suggest</t>
+          <t>/api/v1/ai/macro/generate</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>UI Form 초안 제안</t>
+          <t>Prompt→Macro 생성</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5597,12 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/chat</t>
+          <t>/api/v1/ai/macro/convert</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>표현 간 변환 (from/to)</t>
         </is>
       </c>
     </row>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/ai/learning/jobs</t>
+          <t>/api/v1/ai/ui/suggest</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>학습 잡 실행 (Platform 전용)</t>
+          <t>UI Form 초안 제안</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>INT-05 QR</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>/api/v1/qr/issue</t>
+          <t>/api/v1/ai/chat</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>도면·서류·Project·자산 QR 발급 (APP-001)</t>
+          <t>사내 자료 챗봇</t>
         </is>
       </c>
     </row>
@@ -5662,27 +5662,77 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/ai/learning/jobs</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>학습 잡 실행 (Platform 전용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
           <t>INT-05 QR</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/qr/issue</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>도면·서류·Project·자산 QR 발급 (APP-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>INT-05 QR</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>/api/v1/qr/resolve</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>QR 해석 → 대상 링크·권한 검사</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E107"/>
+  <autoFilter ref="A1:E109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -71,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3C4"/>
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FD"/>
+        <fgColor rgb="00FFF3C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,10 +159,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -811,14 +811,14 @@
           <t>P1~</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>프로토타입 배포</t>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>구축중</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>https://edim.seekerslab.com — Drawing Viewer·DXF/IFC 업로드·AI 생성(샘플 모드)</t>
+          <t>edim-web(React19+Vite+TS, dense B안) — /cpq 셸(MDI·F-key·메뉴트리)·제품선정·기술데이터·Run, mock API(OpenAPI 대응). 루트(/)는 Drawing Viewer 프로토타입 유지</t>
         </is>
       </c>
     </row>
@@ -873,10 +873,14 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr"/>
+          <t>구축중</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>edim-web /plm — Design Editor(CAD 툴바·파라메트릭 치수·커맨드라인)·Work Process(MAKE/BUY) — mock API</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -1055,7 +1059,7 @@
           <t>GW-01</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>게이트웨이</t>
         </is>
@@ -1095,7 +1099,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>개발 대체 구축</t>
         </is>
@@ -1115,7 +1119,7 @@
           <t>SVC-01</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>게이트웨이</t>
         </is>
@@ -2915,7 +2919,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K39" s="8" t="inlineStr">
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>부분 구축</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>edim-web(React19+Vite+TS, dense B안) — /cpq 셸(MDI·F-key·메뉴트리)·제품선정·기술데이터·Run, mock API(OpenAPI 대응). 루트(/)는 Drawing Viewer 프로토타입 유지</t>
+          <t>edim-web(React19+Vite+TS, dense B안) — 셸(4모듈·MDI·F-key)·CPQ 3화면·ERP 5화면(Project·Dashboard·단가·Process·구매발주), mock API(OpenAPI 대응). 루트(/)는 Drawing Viewer 프로토타입 유지</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>edim-web /plm — Design Editor(CAD 툴바·파라메트릭 치수·커맨드라인)·Work Process(MAKE/BUY) — mock API</t>
+          <t>edim-web — Design Editor·Work Process(/plm) + Code Set-up 3화면(/code: Sub Code·Relationship Running Test·데이터 Table) — mock API</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>edim-web(React19+Vite+TS, dense B안) — 셸(4모듈·MDI·F-key)·CPQ 3화면·ERP 5화면(Project·Dashboard·단가·Process·구매발주), mock API(OpenAPI 대응). 루트(/)는 Drawing Viewer 프로토타입 유지</t>
+          <t>edim-web(React19+Vite+TS, dense B안) — 6모듈 셸(MDI·F-key), 와이어프레임 24화면 전량 + 상세 드릴다운 4종, mock API(OpenAPI 대응). 루트(/)는 Drawing Viewer 프로토타입 유지</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>edim-web — Design Editor·Work Process(/plm) + Code Set-up 3화면(/code: Sub Code·Relationship Running Test·데이터 Table) — mock API</t>
+          <t>edim-web /code·/plm — Sub Code·Relationship(Running Test)·데이터 Table·Design Editor·Work Process·Duct — mock API</t>
         </is>
       </c>
     </row>
@@ -933,10 +933,14 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr"/>
+          <t>구축중</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>edim-web /toolbox — Macro Studio(4-Way Sync·TESTED 게이트)·UI Designer(팔레트·Inspector·AI 초안) — mock</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">

--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -1165,10 +1165,14 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr"/>
+          <t>구축중</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/auth/login — sys_user 실검증(sha256)·HMAC 토큰</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1277,10 +1281,14 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr"/>
+          <t>구축중</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1 codes — group slots·BOM expand(재귀 CTE+slot_map, 실 PG)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1393,10 +1401,14 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr"/>
+          <t>구축중</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/tables/tech-data — tbl_data_row(row_key_num) 조회</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1505,10 +1517,14 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr"/>
+          <t>구축중</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/cpq/runs — 202+폴링, cpq_run/cpq_output 영속 (파이프라인 단계는 mock)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1561,10 +1577,14 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr"/>
+          <t>구축중</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>/api/v1/prices/resolve — cst_price 우선순위 resolve(APPLIED→…→QUOTE)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">

--- a/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_컴포넌트정의서.xlsx
@@ -569,14 +569,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C12"/>
+  <dimension ref="B2:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -584,7 +583,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
